--- a/src/nodes/HPC/compressor_stage_5_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_5_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00057059096830565316</v>
       </c>
       <c r="B2">
-        <v>0.00046260783072935127</v>
+        <v>0.00050483156238396954</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0011411819366113063</v>
       </c>
       <c r="B3">
-        <v>0.00077879975334594644</v>
+        <v>0.000837000032113123</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0017117729049169596</v>
       </c>
       <c r="B4">
-        <v>0.0010619694434936388</v>
+        <v>0.0011324944871762175</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0022823638732226126</v>
       </c>
       <c r="B5">
-        <v>0.0013187702894145439</v>
+        <v>0.0013992236159456409</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0028529548415282655</v>
       </c>
       <c r="B6">
-        <v>0.0015521020094258038</v>
+        <v>0.0016405985468988212</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0034235458098339192</v>
       </c>
       <c r="B7">
-        <v>0.0017637257078087574</v>
+        <v>0.001858672044934818</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0039941367781395724</v>
       </c>
       <c r="B8">
-        <v>0.0019547820382396354</v>
+        <v>0.002054756010720997</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0045647277464452253</v>
       </c>
       <c r="B9">
-        <v>0.0021268577820679154</v>
+        <v>0.0022307053382995441</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0051353187147508781</v>
       </c>
       <c r="B10">
-        <v>0.0022816295352628179</v>
+        <v>0.0023884861648653358</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0057059096830565309</v>
       </c>
       <c r="B11">
-        <v>0.0024206870245992843</v>
+        <v>0.0025299666068491831</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0062765006513621846</v>
       </c>
       <c r="B12">
-        <v>0.0025449555263151367</v>
+        <v>0.0026562203592030644</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0068470916196678383</v>
       </c>
       <c r="B13">
-        <v>0.002652789383694</v>
+        <v>0.0027652414517276781</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.00741768258797349</v>
       </c>
       <c r="B14">
-        <v>0.0027432530331068694</v>
+        <v>0.0028558786961446624</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0079882735562791449</v>
       </c>
       <c r="B15">
-        <v>0.0028208222162284169</v>
+        <v>0.0029334796970106845</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.0085588645245847968</v>
       </c>
       <c r="B16">
-        <v>0.002889600888881043</v>
+        <v>0.0030029480786766673</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.00912945549289045</v>
       </c>
       <c r="B17">
-        <v>0.0029467945581743951</v>
+        <v>0.003060912751835526</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.0097000464611961042</v>
       </c>
       <c r="B18">
-        <v>0.0029887563095748713</v>
+        <v>0.003102982316369015</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.010270637429501756</v>
       </c>
       <c r="B19">
-        <v>0.0030153279906886426</v>
+        <v>0.0031289588425722388</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.01084122839780741</v>
       </c>
       <c r="B20">
-        <v>0.0030272236396568205</v>
+        <v>0.0031396927683436438</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.011411819366113062</v>
       </c>
       <c r="B21">
-        <v>0.0030251572946205182</v>
+        <v>0.003136034531581673</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.011982410334418716</v>
       </c>
       <c r="B22">
-        <v>0.0030097111791717659</v>
+        <v>0.003118678484125257</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.012553001302724369</v>
       </c>
       <c r="B23">
-        <v>0.0029809402587062644</v>
+        <v>0.0030876946335752706</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.013123592271030023</v>
       </c>
       <c r="B24">
-        <v>0.002938767684070631</v>
+        <v>0.0030429969014730764</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.013694183239335677</v>
       </c>
       <c r="B25">
-        <v>0.0028831166061114846</v>
+        <v>0.002984499209360033</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.014264774207641327</v>
       </c>
       <c r="B26">
-        <v>0.0028138796739906537</v>
+        <v>0.0029120809900875511</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.014835365175946981</v>
       </c>
       <c r="B27">
-        <v>0.0027308275301308155</v>
+        <v>0.0028254837217472316</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.015405956144252634</v>
       </c>
       <c r="B28">
-        <v>0.0026337003152698568</v>
+        <v>0.0027244143937407237</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.01597654711255829</v>
       </c>
       <c r="B29">
-        <v>0.0025222381701456658</v>
+        <v>0.0026085799954696769</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.016547138080863943</v>
       </c>
       <c r="B30">
-        <v>0.0023962595753565935</v>
+        <v>0.0024777839653272685</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.017117729049169594</v>
       </c>
       <c r="B31">
-        <v>0.0022558963709428457</v>
+        <v>0.0023322155376727838</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.017688320017475247</v>
       </c>
       <c r="B32">
-        <v>0.0021013587368050889</v>
+        <v>0.0021721603958570358</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.0182589109857809</v>
       </c>
       <c r="B33">
-        <v>0.0019328568528439931</v>
+        <v>0.0019979042232308375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.018829501954086555</v>
       </c>
       <c r="B34">
-        <v>0.0017504384734831</v>
+        <v>0.0018095410562778559</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.019400092922392208</v>
       </c>
       <c r="B35">
-        <v>0.0015535016512374486</v>
+        <v>0.0016063983440131704</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.019970683890697859</v>
       </c>
       <c r="B36">
-        <v>0.0013412820131449535</v>
+        <v>0.0013876118885847142</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.020541274859003512</v>
       </c>
       <c r="B37">
-        <v>0.0011130151862435253</v>
+        <v>0.0011523174921404186</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.021111865827309166</v>
       </c>
       <c r="B38">
-        <v>0.00086755885176941047</v>
+        <v>0.00089920132340378712</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.02168245679561482</v>
       </c>
       <c r="B39">
-        <v>0.0006022589077521812</v>
+        <v>0.000625151017400604</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.022253047763920474</v>
       </c>
       <c r="B40">
-        <v>0.00031408330641974238</v>
+        <v>0.00032660457573222305</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.022253047763920474</v>
       </c>
       <c r="B43">
-        <v>0.00018887061329493678</v>
+        <v>0.0001763493439824562</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.02168245679561482</v>
       </c>
       <c r="B44">
-        <v>0.0003733378112679537</v>
+        <v>0.00035044570161953093</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.021111865827309166</v>
       </c>
       <c r="B45">
-        <v>0.0005511341354256414</v>
+        <v>0.00051949166379126443</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.020541274859003512</v>
       </c>
       <c r="B46">
-        <v>0.0007199921272745915</v>
+        <v>0.000680689821377698</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.019970683890697859</v>
       </c>
       <c r="B47">
-        <v>0.000877983258747344</v>
+        <v>0.00083165338330758285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.019400092922392208</v>
       </c>
       <c r="B48">
-        <v>0.0010245347234802322</v>
+        <v>0.00097163803070451048</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.018829501954086555</v>
       </c>
       <c r="B49">
-        <v>0.0011594126455355396</v>
+        <v>0.0011003100627407837</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.0182589109857809</v>
       </c>
       <c r="B50">
-        <v>0.0012823831489755485</v>
+        <v>0.0012173357785887039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.017688320017475247</v>
       </c>
       <c r="B51">
-        <v>0.0013933421462856239</v>
+        <v>0.0013225404872336773</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.017117729049169594</v>
       </c>
       <c r="B52">
-        <v>0.001492704703643463</v>
+        <v>0.0014163855369135248</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.016547138080863943</v>
       </c>
       <c r="B53">
-        <v>0.0015810156756498454</v>
+        <v>0.0014994912856791706</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.01597654711255829</v>
       </c>
       <c r="B54">
-        <v>0.0016588199169055517</v>
+        <v>0.0015724780915815403</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.015405956144252634</v>
       </c>
       <c r="B55">
-        <v>0.0017265595305611865</v>
+        <v>0.0016358454520903197</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.014835365175946981</v>
       </c>
       <c r="B56">
-        <v>0.0017842656139666535</v>
+        <v>0.0016896094223502376</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.014264774207641327</v>
       </c>
       <c r="B57">
-        <v>0.0018318665130216817</v>
+        <v>0.0017336651969247848</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.013694183239335677</v>
       </c>
       <c r="B58">
-        <v>0.0018692905736259998</v>
+        <v>0.0017679079703774518</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.013123592271030023</v>
       </c>
       <c r="B59">
-        <v>0.0018964755100461838</v>
+        <v>0.0017922462926437393</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.012553001302724369</v>
       </c>
       <c r="B60">
-        <v>0.0019133965100161989</v>
+        <v>0.0018066421351471927</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.011982410334418716</v>
       </c>
       <c r="B61">
-        <v>0.0019200381296368577</v>
+        <v>0.0018110708246833671</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.011411819366113062</v>
       </c>
       <c r="B62">
-        <v>0.001916384925008973</v>
+        <v>0.0018055076880478186</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.01084122839780741</v>
       </c>
       <c r="B63">
-        <v>0.0019025323527885891</v>
+        <v>0.001790063224101766</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.010270637429501756</v>
       </c>
       <c r="B64">
-        <v>0.0018790194718526778</v>
+        <v>0.0017653886199690814</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.0097000464611961042</v>
       </c>
       <c r="B65">
-        <v>0.0018464962416334435</v>
+        <v>0.0017322702348393003</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.00912945549289045</v>
       </c>
       <c r="B66">
-        <v>0.0018056126215630893</v>
+        <v>0.0016914944279019586</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.0085588645245847968</v>
       </c>
       <c r="B67">
-        <v>0.0017561289909248067</v>
+        <v>0.0016427818011291828</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0079882735562791449</v>
       </c>
       <c r="B68">
-        <v>0.0016942474084057347</v>
+        <v>0.0015815899276234665</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.00741768258797349</v>
       </c>
       <c r="B69">
-        <v>0.001616996402728936</v>
+        <v>0.0015043707396911431</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0068470916196678383</v>
       </c>
       <c r="B70">
-        <v>0.0015282687033572188</v>
+        <v>0.0014158166353235406</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0062765006513621846</v>
       </c>
       <c r="B71">
-        <v>0.0014323071974358627</v>
+        <v>0.0013210423645479354</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0057059096830565309</v>
       </c>
       <c r="B72">
-        <v>0.0013278912021002975</v>
+        <v>0.001218611619850399</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0051353187147508781</v>
       </c>
       <c r="B73">
-        <v>0.0012130632392376428</v>
+        <v>0.0011062066096351256</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0045647277464452253</v>
       </c>
       <c r="B74">
-        <v>0.0010883822197516263</v>
+        <v>0.00098453466351999743</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0039941367781395724</v>
       </c>
       <c r="B75">
-        <v>0.00095504231342601823</v>
+        <v>0.00085506834094465657</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0034235458098339192</v>
       </c>
       <c r="B76">
-        <v>0.00081426233654815063</v>
+        <v>0.00071931599942209</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0028529548415282655</v>
       </c>
       <c r="B77">
-        <v>0.00066713663469562671</v>
+        <v>0.00057864009722260914</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0022823638732226126</v>
       </c>
       <c r="B78">
-        <v>0.00051423702410357294</v>
+        <v>0.00043378369757247594</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0017117729049169596</v>
       </c>
       <c r="B79">
-        <v>0.00035671900666785157</v>
+        <v>0.00028619396298527287</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0011411819366113063</v>
       </c>
       <c r="B80">
-        <v>0.00019679696567418035</v>
+        <v>0.00013859668690700377</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00057059096830565316</v>
       </c>
       <c r="B81">
-        <v>4.0370514183167975E-05</v>
+        <v>-1.8532174714503338E-06</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00061919511170993244</v>
       </c>
       <c r="B2">
-        <v>0.00059068393951932318</v>
+        <v>0.00068232481605239308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0012383902234198649</v>
       </c>
       <c r="B3">
-        <v>0.000965745641792163</v>
+        <v>0.0010920614445809893</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0018575853351297973</v>
       </c>
       <c r="B4">
-        <v>0.0012972624387415004</v>
+        <v>0.0014503274703561958</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0024767804468397298</v>
       </c>
       <c r="B5">
-        <v>0.001595165090145503</v>
+        <v>0.0017697781116477035</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0030959755585496618</v>
       </c>
       <c r="B6">
-        <v>0.0018636979821226832</v>
+        <v>0.0020557677008890482</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0037151706702595946</v>
       </c>
       <c r="B7">
-        <v>0.0021053946908973242</v>
+        <v>0.0023114628240743893</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0043343657819695271</v>
       </c>
       <c r="B8">
-        <v>0.002321854917551647</v>
+        <v>0.0025388348506287586</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0049535608936794595</v>
       </c>
       <c r="B9">
-        <v>0.0025153742778673866</v>
+        <v>0.002740761298529802</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0055727560053893911</v>
       </c>
       <c r="B10">
-        <v>0.0026883930402112509</v>
+        <v>0.0029203108460613934</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0061919511170993235</v>
       </c>
       <c r="B11">
-        <v>0.0028432341685903344</v>
+        <v>0.0030804106641797073</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0068111462288092568</v>
       </c>
       <c r="B12">
-        <v>0.0029812180260710267</v>
+        <v>0.0032227032386183165</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0074303413405191893</v>
       </c>
       <c r="B13">
-        <v>0.0030997718763164975</v>
+        <v>0.0033438338215480844</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0080495364522291217</v>
       </c>
       <c r="B14">
-        <v>0.0031974080479936638</v>
+        <v>0.0034418467576114264</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0086687315639390541</v>
       </c>
       <c r="B15">
-        <v>0.0032808722291876409</v>
+        <v>0.0035253799948996595</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.0092879266756489848</v>
       </c>
       <c r="B16">
-        <v>0.0033563503184691431</v>
+        <v>0.0036023550039478375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.009907121787358919</v>
       </c>
       <c r="B17">
-        <v>0.0034195556969330819</v>
+        <v>0.0036672337416170544</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.010526316899068852</v>
       </c>
       <c r="B18">
-        <v>0.003464912732873868</v>
+        <v>0.0037128247713244696</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.011145512010778782</v>
       </c>
       <c r="B19">
-        <v>0.0034921622608596989</v>
+        <v>0.0037387825963854722</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.011764707122488716</v>
       </c>
       <c r="B20">
-        <v>0.0035023742320272212</v>
+        <v>0.00374647320509001</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.012383902234198647</v>
       </c>
       <c r="B21">
-        <v>0.0034966185975130793</v>
+        <v>0.0037372625857280272</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.01300309734590858</v>
       </c>
       <c r="B22">
-        <v>0.0034757698963805879</v>
+        <v>0.0037122686364982676</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.013622292457618514</v>
       </c>
       <c r="B23">
-        <v>0.00343992101939973</v>
+        <v>0.0036716168952346559</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.014241487569328446</v>
       </c>
       <c r="B24">
-        <v>0.0033889694452671577</v>
+        <v>0.0036151848096799138</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.014860682681038379</v>
       </c>
       <c r="B25">
-        <v>0.0033228126526795225</v>
+        <v>0.003542849827576763</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.015479877792748309</v>
       </c>
       <c r="B26">
-        <v>0.0032413066894963227</v>
+        <v>0.0034544393125774094</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.016099072904458243</v>
       </c>
       <c r="B27">
-        <v>0.0031441418802284427</v>
+        <v>0.0033495802919719922</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.016718268016168176</v>
       </c>
       <c r="B28">
-        <v>0.0030309671185496153</v>
+        <v>0.0032278497089601355</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.017337463127878108</v>
       </c>
       <c r="B29">
-        <v>0.0029014312981335715</v>
+        <v>0.0030888245067414652</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.017956658239588041</v>
       </c>
       <c r="B30">
-        <v>0.002755308032999693</v>
+        <v>0.0029322456522714205</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.01857585335129797</v>
       </c>
       <c r="B31">
-        <v>0.0025928698185499616</v>
+        <v>0.0027585102075287048</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.019195048463007902</v>
       </c>
       <c r="B32">
-        <v>0.0024145138705320059</v>
+        <v>0.0025681792582478327</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.019814243574717838</v>
       </c>
       <c r="B33">
-        <v>0.0022206374046934586</v>
+        <v>0.0023618138901633232</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.02043343868642777</v>
       </c>
       <c r="B34">
-        <v>0.0020113985735298228</v>
+        <v>0.0021396727046981271</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.021052633798137703</v>
       </c>
       <c r="B35">
-        <v>0.0017859992765280968</v>
+        <v>0.001900804366028931</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.021671828909847632</v>
       </c>
       <c r="B36">
-        <v>0.0015434023499231531</v>
+        <v>0.001643955054020856</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.022291024021557564</v>
       </c>
       <c r="B37">
-        <v>0.0012825706299498607</v>
+        <v>0.001367870948539021</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.022910219133267497</v>
       </c>
       <c r="B38">
-        <v>0.001001902069388863</v>
+        <v>0.001070577757742664</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.023529414244977433</v>
       </c>
       <c r="B39">
-        <v>0.00069753508720388734</v>
+        <v>0.00074721930296749227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.024148609356687365</v>
       </c>
       <c r="B40">
-        <v>0.00036504321890443295</v>
+        <v>0.000392218933843329</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.024767804468397294</v>
       </c>
       <c r="B41">
-        <v>8.59305837194641E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.024767804468397294</v>
       </c>
       <c r="B42">
-        <v>4.2965291859732049E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.024148609356687365</v>
       </c>
       <c r="B43">
-        <v>0.00017481321433216045</v>
+        <v>0.00014763749939326437</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.023529414244977433</v>
       </c>
       <c r="B44">
-        <v>0.00034974557685865318</v>
+        <v>0.0003000613610950483</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.022910219133267497</v>
       </c>
       <c r="B45">
-        <v>0.00052117225091225373</v>
+        <v>0.00045249656255845255</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.022291024021557564</v>
       </c>
       <c r="B46">
-        <v>0.00068546839982573866</v>
+        <v>0.00060016808123657844</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.021671828909847632</v>
       </c>
       <c r="B47">
-        <v>0.00083953342123923344</v>
+        <v>0.00073898071714153081</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.021052633798137703</v>
       </c>
       <c r="B48">
-        <v>0.000982363650022261</v>
+        <v>0.00086755856052142717</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.02043343868642777</v>
       </c>
       <c r="B49">
-        <v>0.0011134796553516947</v>
+        <v>0.00098520552418339055</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.019814243574717838</v>
       </c>
       <c r="B50">
-        <v>0.0012324020064044066</v>
+        <v>0.001091225520934542</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.019195048463007902</v>
       </c>
       <c r="B51">
-        <v>0.0013388561565212196</v>
+        <v>0.0011851907688053929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.01857585335129797</v>
       </c>
       <c r="B52">
-        <v>0.0014333870956987585</v>
+        <v>0.0012677467067200153</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.017956658239588041</v>
       </c>
       <c r="B53">
-        <v>0.0015167446980975982</v>
+        <v>0.0013398070788258702</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.017337463127878108</v>
       </c>
       <c r="B54">
-        <v>0.001589678837878314</v>
+        <v>0.0014022856292704204</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.016718268016168176</v>
       </c>
       <c r="B55">
-        <v>0.0016527889856759719</v>
+        <v>0.0014559063952654515</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.016099072904458243</v>
       </c>
       <c r="B56">
-        <v>0.0017060729980235988</v>
+        <v>0.0015006345862800497</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.015479877792748309</v>
       </c>
       <c r="B57">
-        <v>0.0017493783279287126</v>
+        <v>0.0015362457048476255</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.014860682681038379</v>
       </c>
       <c r="B58">
-        <v>0.0017825524283988311</v>
+        <v>0.0015625152535015895</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.014241487569328446</v>
       </c>
       <c r="B59">
-        <v>0.0018054618943778588</v>
+        <v>0.0015792465299651018</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.013622292457618514</v>
       </c>
       <c r="B60">
-        <v>0.0018180498885552452</v>
+        <v>0.001586354012720319</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.01300309734590858</v>
       </c>
       <c r="B61">
-        <v>0.0018202787155568278</v>
+        <v>0.0015837799754391481</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.012383902234198647</v>
       </c>
       <c r="B62">
-        <v>0.0018121106800084424</v>
+        <v>0.0015714666917934946</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.011764707122488716</v>
       </c>
       <c r="B63">
-        <v>0.0017936814205876961</v>
+        <v>0.0015495824475249074</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.011145512010778782</v>
       </c>
       <c r="B64">
-        <v>0.0017658199121792786</v>
+        <v>0.0015191995766535048</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.010526316899068852</v>
       </c>
       <c r="B65">
-        <v>0.0017295284637196505</v>
+        <v>0.0014816164252690481</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.009907121787358919</v>
       </c>
       <c r="B66">
-        <v>0.0016858093841452711</v>
+        <v>0.0014381313394612983</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.0092879266756489848</v>
       </c>
       <c r="B67">
-        <v>0.0016343175201182778</v>
+        <v>0.001388312834639583</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0086687315639390541</v>
       </c>
       <c r="B68">
-        <v>0.0015693178692035143</v>
+        <v>0.0013248101034914962</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0080495364522291217</v>
       </c>
       <c r="B69">
-        <v>0.0014863370806693296</v>
+        <v>0.0012418983710515675</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0074303413405191893</v>
       </c>
       <c r="B70">
-        <v>0.0013913382596953893</v>
+        <v>0.0011472763144638025</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0068111462288092568</v>
       </c>
       <c r="B71">
-        <v>0.0012908215382400007</v>
+        <v>0.0010493363256927114</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0061919511170993235</v>
       </c>
       <c r="B72">
-        <v>0.0011829986994647275</v>
+        <v>0.00094582220387535521</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0055727560053893911</v>
       </c>
       <c r="B73">
-        <v>0.0010649683992602522</v>
+        <v>0.00083305059341010957</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0049535608936794595</v>
       </c>
       <c r="B74">
-        <v>0.0009376651332304788</v>
+        <v>0.00071227811256806349</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0043343657819695271</v>
       </c>
       <c r="B75">
-        <v>0.00080299538601186573</v>
+        <v>0.00058601545293475443</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0037151706702595946</v>
       </c>
       <c r="B76">
-        <v>0.00066291775865786533</v>
+        <v>0.00045684962548079992</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0030959755585496618</v>
       </c>
       <c r="B77">
-        <v>0.0005192099507581266</v>
+        <v>0.00032714023199176154</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0024767804468397298</v>
       </c>
       <c r="B78">
-        <v>0.00037287393963009657</v>
+        <v>0.0001982609181278958</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0018575853351297973</v>
       </c>
       <c r="B79">
-        <v>0.00022580721743863328</v>
+        <v>7.2742185823938108E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0012383902234198649</v>
       </c>
       <c r="B80">
-        <v>8.1535022270379725E-05</v>
+        <v>-4.4780780518446406E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00061919511170993244</v>
       </c>
       <c r="B81">
-        <v>-5.0802196212166814E-05</v>
+        <v>-0.00014244307274523672</v>
       </c>
     </row>
     <row r="82" spans="1:2">
